--- a/artfynd/A 29125-2023 artfynd.xlsx
+++ b/artfynd/A 29125-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117857024</v>
+        <v>118087759</v>
       </c>
       <c r="B2" t="n">
         <v>57990</v>
@@ -708,7 +708,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sållaretorp, Nrk</t>
@@ -721,7 +725,7 @@
         <v>6545536</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,15 +769,333 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>118087771</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57284</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102119</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Göktyta</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Jynx torquilla</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sållaretorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>499827</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6545739</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mats Wilhelm</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mats Wilhelm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118087770</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57284</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102119</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Göktyta</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Jynx torquilla</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sållaretorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>499863</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6545682</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mats Wilhelm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mats Wilhelm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118087756</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57990</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sållaretorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>499863</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6545732</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mats Wilhelm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mats Wilhelm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29125-2023 artfynd.xlsx
+++ b/artfynd/A 29125-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118087759</v>
       </c>
       <c r="B2" t="n">
-        <v>57990</v>
+        <v>57991</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118087771</v>
+        <v>118087756</v>
       </c>
       <c r="B3" t="n">
-        <v>57284</v>
+        <v>57991</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,20 +793,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102119</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499827</v>
+        <v>499863</v>
       </c>
       <c r="R3" t="n">
-        <v>6545739</v>
+        <v>6545732</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
         <v>118087770</v>
       </c>
       <c r="B4" t="n">
-        <v>57284</v>
+        <v>57285</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118087756</v>
+        <v>118087771</v>
       </c>
       <c r="B5" t="n">
-        <v>57990</v>
+        <v>57285</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,20 +1005,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>102119</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499863</v>
+        <v>499827</v>
       </c>
       <c r="R5" t="n">
-        <v>6545732</v>
+        <v>6545739</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 29125-2023 artfynd.xlsx
+++ b/artfynd/A 29125-2023 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>129531028</v>
       </c>
       <c r="B6" t="n">
-        <v>56603</v>
+        <v>56608</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>129531031</v>
       </c>
       <c r="B7" t="n">
-        <v>56596</v>
+        <v>56601</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129530875</v>
+        <v>129530874</v>
       </c>
       <c r="B8" t="n">
-        <v>56603</v>
+        <v>56615</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,26 +1362,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1477,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129530846</v>
+        <v>129530875</v>
       </c>
       <c r="B9" t="n">
-        <v>56615</v>
+        <v>56608</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,26 +1488,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499731</v>
+        <v>499799</v>
       </c>
       <c r="R9" t="n">
-        <v>6545684</v>
+        <v>6545520</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129530874</v>
+        <v>129530846</v>
       </c>
       <c r="B10" t="n">
-        <v>56610</v>
+        <v>56620</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,26 +1614,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499799</v>
+        <v>499731</v>
       </c>
       <c r="R10" t="n">
-        <v>6545520</v>
+        <v>6545684</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1732,7 +1732,7 @@
         <v>129530873</v>
       </c>
       <c r="B11" t="n">
-        <v>56615</v>
+        <v>56620</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>129531051</v>
       </c>
       <c r="B12" t="n">
-        <v>56610</v>
+        <v>56615</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>129530876</v>
       </c>
       <c r="B13" t="n">
-        <v>56596</v>
+        <v>56601</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>129530847</v>
       </c>
       <c r="B14" t="n">
-        <v>56610</v>
+        <v>56615</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>129531027</v>
       </c>
       <c r="B15" t="n">
-        <v>56610</v>
+        <v>56615</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>129531026</v>
       </c>
       <c r="B16" t="n">
-        <v>56617</v>
+        <v>56622</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>129525981</v>
       </c>
       <c r="B17" t="n">
-        <v>56596</v>
+        <v>56601</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 29125-2023 artfynd.xlsx
+++ b/artfynd/A 29125-2023 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>129531028</v>
       </c>
       <c r="B6" t="n">
-        <v>56608</v>
+        <v>56609</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>129531031</v>
       </c>
       <c r="B7" t="n">
-        <v>56601</v>
+        <v>56602</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>129530874</v>
       </c>
       <c r="B8" t="n">
-        <v>56615</v>
+        <v>56616</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>129530875</v>
       </c>
       <c r="B9" t="n">
-        <v>56608</v>
+        <v>56609</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>129530846</v>
       </c>
       <c r="B10" t="n">
-        <v>56620</v>
+        <v>56621</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>129530873</v>
       </c>
       <c r="B11" t="n">
-        <v>56620</v>
+        <v>56621</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>129531051</v>
       </c>
       <c r="B12" t="n">
-        <v>56615</v>
+        <v>56616</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>129530876</v>
       </c>
       <c r="B13" t="n">
-        <v>56601</v>
+        <v>56602</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>129530847</v>
       </c>
       <c r="B14" t="n">
-        <v>56615</v>
+        <v>56616</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>129531027</v>
       </c>
       <c r="B15" t="n">
-        <v>56615</v>
+        <v>56616</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>129531026</v>
       </c>
       <c r="B16" t="n">
-        <v>56622</v>
+        <v>56623</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>129525981</v>
       </c>
       <c r="B17" t="n">
-        <v>56601</v>
+        <v>56602</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 29125-2023 artfynd.xlsx
+++ b/artfynd/A 29125-2023 artfynd.xlsx
@@ -1729,10 +1729,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129530873</v>
+        <v>129531051</v>
       </c>
       <c r="B11" t="n">
-        <v>56621</v>
+        <v>56616</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,26 +1740,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499799</v>
+        <v>499798</v>
       </c>
       <c r="R11" t="n">
-        <v>6545520</v>
+        <v>6545509</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1813,22 +1813,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129531051</v>
+        <v>129530873</v>
       </c>
       <c r="B12" t="n">
-        <v>56616</v>
+        <v>56621</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,26 +1866,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499798</v>
+        <v>499799</v>
       </c>
       <c r="R12" t="n">
-        <v>6545509</v>
+        <v>6545520</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1939,22 +1939,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 29125-2023 artfynd.xlsx
+++ b/artfynd/A 29125-2023 artfynd.xlsx
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129530874</v>
+        <v>129530846</v>
       </c>
       <c r="B8" t="n">
-        <v>56616</v>
+        <v>56621</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,26 +1362,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499799</v>
+        <v>499731</v>
       </c>
       <c r="R8" t="n">
-        <v>6545520</v>
+        <v>6545684</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129530846</v>
+        <v>129530874</v>
       </c>
       <c r="B10" t="n">
-        <v>56621</v>
+        <v>56616</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,26 +1614,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499731</v>
+        <v>499799</v>
       </c>
       <c r="R10" t="n">
-        <v>6545684</v>
+        <v>6545520</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1729,10 +1729,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129531051</v>
+        <v>129530873</v>
       </c>
       <c r="B11" t="n">
-        <v>56616</v>
+        <v>56621</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,26 +1740,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499798</v>
+        <v>499799</v>
       </c>
       <c r="R11" t="n">
-        <v>6545509</v>
+        <v>6545520</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1813,22 +1813,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129530873</v>
+        <v>129531051</v>
       </c>
       <c r="B12" t="n">
-        <v>56621</v>
+        <v>56616</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,26 +1866,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499799</v>
+        <v>499798</v>
       </c>
       <c r="R12" t="n">
-        <v>6545520</v>
+        <v>6545509</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1939,22 +1939,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 29125-2023 artfynd.xlsx
+++ b/artfynd/A 29125-2023 artfynd.xlsx
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129530846</v>
+        <v>129530874</v>
       </c>
       <c r="B8" t="n">
-        <v>56621</v>
+        <v>56616</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,26 +1362,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499731</v>
+        <v>499799</v>
       </c>
       <c r="R8" t="n">
-        <v>6545684</v>
+        <v>6545520</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129530874</v>
+        <v>129530846</v>
       </c>
       <c r="B10" t="n">
-        <v>56616</v>
+        <v>56621</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,26 +1614,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499799</v>
+        <v>499731</v>
       </c>
       <c r="R10" t="n">
-        <v>6545520</v>
+        <v>6545684</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1729,10 +1729,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129531051</v>
+        <v>129530873</v>
       </c>
       <c r="B11" t="n">
-        <v>56616</v>
+        <v>56621</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,26 +1740,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499798</v>
+        <v>499799</v>
       </c>
       <c r="R11" t="n">
-        <v>6545509</v>
+        <v>6545520</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1813,22 +1813,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129530873</v>
+        <v>129531051</v>
       </c>
       <c r="B12" t="n">
-        <v>56621</v>
+        <v>56616</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,26 +1866,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499799</v>
+        <v>499798</v>
       </c>
       <c r="R12" t="n">
-        <v>6545520</v>
+        <v>6545509</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1939,22 +1939,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 29125-2023 artfynd.xlsx
+++ b/artfynd/A 29125-2023 artfynd.xlsx
@@ -1729,10 +1729,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129531051</v>
+        <v>129530873</v>
       </c>
       <c r="B11" t="n">
-        <v>56616</v>
+        <v>56621</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,26 +1740,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499798</v>
+        <v>499799</v>
       </c>
       <c r="R11" t="n">
-        <v>6545509</v>
+        <v>6545520</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1813,22 +1813,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129530873</v>
+        <v>129531051</v>
       </c>
       <c r="B12" t="n">
-        <v>56621</v>
+        <v>56616</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,26 +1866,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499799</v>
+        <v>499798</v>
       </c>
       <c r="R12" t="n">
-        <v>6545520</v>
+        <v>6545509</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1939,22 +1939,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 29125-2023 artfynd.xlsx
+++ b/artfynd/A 29125-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118087759</v>
+        <v>129530847</v>
       </c>
       <c r="B2" t="n">
-        <v>57993</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +729,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499862</v>
+        <v>499731</v>
       </c>
       <c r="R2" t="n">
-        <v>6545536</v>
+        <v>6545684</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,27 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mats Wilhelm</t>
+          <t>Julius Stölzle</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mats Wilhelm</t>
+          <t>Julius Stölzle</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118087770</v>
+        <v>129530874</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,26 +812,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102119</v>
+        <v>100092</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,13 +855,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499863</v>
+        <v>499799</v>
       </c>
       <c r="R3" t="n">
-        <v>6545682</v>
+        <v>6545520</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,12 +885,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,27 +915,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mats Wilhelm</t>
+          <t>Julius Stölzle</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mats Wilhelm</t>
+          <t>Julius Stölzle</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118087771</v>
+        <v>129530891</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,26 +938,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102119</v>
+        <v>100092</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,13 +981,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499827</v>
+        <v>499909</v>
       </c>
       <c r="R4" t="n">
-        <v>6545739</v>
+        <v>6545644</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,12 +1011,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,54 +1041,64 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mats Wilhelm</t>
+          <t>Julius Stölzle</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mats Wilhelm</t>
+          <t>Julius Stölzle</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118087756</v>
+        <v>129531027</v>
       </c>
       <c r="B5" t="n">
-        <v>57993</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>100092</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1037,13 +1107,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499863</v>
+        <v>499766</v>
       </c>
       <c r="R5" t="n">
-        <v>6545732</v>
+        <v>6545709</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,12 +1137,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,22 +1167,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mats Wilhelm</t>
+          <t>Julius Stölzle</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mats Wilhelm</t>
+          <t>Julius Stölzle</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129531028</v>
+        <v>129531051</v>
       </c>
       <c r="B6" t="n">
-        <v>56609</v>
+        <v>56830</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,26 +1190,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1153,10 +1233,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499766</v>
+        <v>499798</v>
       </c>
       <c r="R6" t="n">
-        <v>6545709</v>
+        <v>6545509</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,37 +1305,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129531031</v>
+        <v>129531071</v>
       </c>
       <c r="B7" t="n">
-        <v>56602</v>
+        <v>56830</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1279,10 +1359,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499766</v>
+        <v>499907</v>
       </c>
       <c r="R7" t="n">
-        <v>6545709</v>
+        <v>6545648</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1351,52 +1431,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129530874</v>
+        <v>118087770</v>
       </c>
       <c r="B8" t="n">
-        <v>56616</v>
+        <v>57942</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100092</v>
+        <v>102119</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1405,13 +1470,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499799</v>
+        <v>499863</v>
       </c>
       <c r="R8" t="n">
-        <v>6545520</v>
+        <v>6545682</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,22 +1500,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>04:30</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,64 +1520,49 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Julius Stölzle</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Julius Stölzle</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129530875</v>
+        <v>118087771</v>
       </c>
       <c r="B9" t="n">
-        <v>56609</v>
+        <v>57942</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205992</v>
+        <v>102119</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1531,13 +1571,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499799</v>
+        <v>499827</v>
       </c>
       <c r="R9" t="n">
-        <v>6545520</v>
+        <v>6545739</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1561,22 +1601,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>04:30</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,44 +1621,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Julius Stölzle</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Julius Stölzle</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129530846</v>
+        <v>118087759</v>
       </c>
       <c r="B10" t="n">
-        <v>56621</v>
+        <v>58676</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205995</v>
+        <v>103055</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1636,34 +1666,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sållaretorp, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499731</v>
+        <v>499862</v>
       </c>
       <c r="R10" t="n">
-        <v>6545684</v>
+        <v>6545536</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1687,22 +1702,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>04:30</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,64 +1722,49 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Julius Stölzle</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Julius Stölzle</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129531051</v>
+        <v>118087756</v>
       </c>
       <c r="B11" t="n">
-        <v>56616</v>
+        <v>58676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100092</v>
+        <v>103055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1783,13 +1773,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499798</v>
+        <v>499863</v>
       </c>
       <c r="R11" t="n">
-        <v>6545509</v>
+        <v>6545732</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1813,22 +1803,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>06:30</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,22 +1823,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Julius Stölzle</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Julius Stölzle</t>
+          <t>Mats Wilhelm</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129530873</v>
+        <v>129530875</v>
       </c>
       <c r="B12" t="n">
-        <v>56621</v>
+        <v>56823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,26 +1846,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1981,37 +1961,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129530876</v>
+        <v>129530892</v>
       </c>
       <c r="B13" t="n">
-        <v>56602</v>
+        <v>56823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2035,10 +2015,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499799</v>
+        <v>499909</v>
       </c>
       <c r="R13" t="n">
-        <v>6545520</v>
+        <v>6545644</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2107,10 +2087,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129530847</v>
+        <v>129531028</v>
       </c>
       <c r="B14" t="n">
-        <v>56616</v>
+        <v>56823</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,26 +2098,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2161,10 +2141,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499731</v>
+        <v>499766</v>
       </c>
       <c r="R14" t="n">
-        <v>6545684</v>
+        <v>6545709</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2191,22 +2171,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2233,10 +2213,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129531027</v>
+        <v>129530846</v>
       </c>
       <c r="B15" t="n">
-        <v>56616</v>
+        <v>56835</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,26 +2224,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2287,10 +2267,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499766</v>
+        <v>499731</v>
       </c>
       <c r="R15" t="n">
-        <v>6545709</v>
+        <v>6545684</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2317,22 +2297,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2359,37 +2339,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129531026</v>
+        <v>129530873</v>
       </c>
       <c r="B16" t="n">
-        <v>56623</v>
+        <v>56835</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2413,10 +2393,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499766</v>
+        <v>499799</v>
       </c>
       <c r="R16" t="n">
-        <v>6545709</v>
+        <v>6545520</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2443,22 +2423,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2485,37 +2465,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129525981</v>
+        <v>129530890</v>
       </c>
       <c r="B17" t="n">
-        <v>56602</v>
+        <v>56835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2530,7 +2510,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>detektor med heterodyn och tidsexpansion</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2539,10 +2519,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499767</v>
+        <v>499909</v>
       </c>
       <c r="R17" t="n">
-        <v>6545535</v>
+        <v>6545644</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2579,12 +2559,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>23:55</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2608,6 +2588,888 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129525975</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn och tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sållaretorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>499898</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6545709</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>23:55</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Julius Stölzle</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Julius Stölzle</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129525981</v>
+      </c>
+      <c r="B19" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn och tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sållaretorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>499767</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6545535</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>23:55</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Julius Stölzle</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Julius Stölzle</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129525982</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn och tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sållaretorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>499903</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6545607</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>23:55</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Julius Stölzle</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Julius Stölzle</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129530876</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sållaretorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>499799</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6545520</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Julius Stölzle</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Julius Stölzle</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129530894</v>
+      </c>
+      <c r="B22" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sållaretorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>499909</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6545644</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Julius Stölzle</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Julius Stölzle</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129531031</v>
+      </c>
+      <c r="B23" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sållaretorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>499766</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6545709</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Julius Stölzle</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Julius Stölzle</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129531026</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sållaretorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>499766</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6545709</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Julius Stölzle</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Julius Stölzle</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29125-2023 artfynd.xlsx
+++ b/artfynd/A 29125-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129530847</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129530874</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129530891</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,6 +1196,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129531027</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1302,6 +1327,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129531051</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1428,6 +1458,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129531071</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1529,6 +1564,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118087770</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1630,6 +1670,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118087771</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1731,6 +1776,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118087759</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1832,6 +1882,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118087756</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1958,6 +2013,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129530875</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2084,6 +2144,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129530892</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2210,6 +2275,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129531028</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2336,6 +2406,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129530846</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2462,6 +2537,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129530873</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2588,6 +2668,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129530890</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2714,6 +2799,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129525975</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2840,6 +2930,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129525981</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2966,6 +3061,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129525982</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3092,6 +3192,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129530876</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3218,6 +3323,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129530894</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3344,6 +3454,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129531031</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3470,8 +3585,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129531026</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>